--- a/config/unlock.xlsx
+++ b/config/unlock.xlsx
@@ -1547,7 +1547,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>ステージ自動戦闘</t>
+          <t>自动战斗关卡</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>ステージ2倍速</t>
+          <t>关卡速度2倍</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>ステージ一時停止</t>
+          <t>关卡暂停</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>ハードステージ</t>
+          <t>困难关卡</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>必殺スキル加速</t>
+          <t>必杀技能加速</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>ハード+ステージ</t>
+          <t>硬+关卡</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>ステージ3倍速</t>
+          <t>关卡3倍速度</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>チュートリアルをスキップ</t>
+          <t>跳过教程</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>一般ショップ</t>
+          <t>一般商店</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>アリーナショップ</t>
+          <t>竞技场商店</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>ギルドショップ</t>
+          <t>公会商店</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>欠片ショップ</t>
+          <t>碎片商店</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>ショップ種類</t>
+          <t>商店类型</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>装飾ガチャ</t>
+          <t>装饰扭蛋</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>ガチャ累計宝箱機能</t>
+          <t>扭蛋累计宝箱功能</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>ダイヤガチャヒント</t>
+          <t>钻石扭蛋提示</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>個人立絵</t>
+          <t>个人立画</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>キャラロック</t>
+          <t>角色摇滚</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>装飾</t>
+          <t>装饰</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>装飾星ランクUP</t>
+          <t>装饰星级提升</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>装飾覚醒</t>
+          <t>装饰觉醒</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>装備道具</t>
+          <t>装备工具</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>個人値洗練</t>
+          <t>个人价值洗练</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>キャラ好感度</t>
+          <t>角色好感度</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>キャラ継承</t>
+          <t>角色继承</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>強化値</t>
+          <t>强化值</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>強化値10回強化</t>
+          <t>强化值10次强化</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>パートナー再生</t>
+          <t>合作伙伴播放</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>一括レベルアップ</t>
+          <t>一次性升级</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>キャラ潜能</t>
+          <t>角色潜能</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>高速レベルアップ</t>
+          <t>快速升级</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>高速強化</t>
+          <t>快速强化</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>ランクスキル効果</t>
+          <t>等级技能效果</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3607,7 +3607,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>極限強化</t>
+          <t>极限强化</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>ルーン</t>
+          <t>符文</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>ルーン一括強化</t>
+          <t>符文一括强化</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>超進化</t>
+          <t>超进化</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>キャラ分岐切替</t>
+          <t>角色分支切换</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>装飾ランク潜能</t>
+          <t>装饰等级潜能</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>強化値設定</t>
+          <t>增强值设置</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>潜能一括強化</t>
+          <t>潜能一一揽子强化</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>装飾覚醒潜能</t>
+          <t>装饰觉醒潜能</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>オンラインパック</t>
+          <t>在线包</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>図鑑</t>
+          <t>图鉴</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>毎日任務</t>
+          <t>每日任务</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>冒険許可証</t>
+          <t>冒险许可证</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>アリーナ</t>
+          <t>竞技场</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>日常ダンジョン</t>
+          <t>日常地牢</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>順位</t>
+          <t>排名</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>ギルド祝封</t>
+          <t>公会祝封</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>ギルド</t>
+          <t>公会</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>試練の道</t>
+          <t>考验之路</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>天賦</t>
+          <t>天赋</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>派遣任務</t>
+          <t>派遣任务</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>探査機</t>
+          <t>探测器</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>カード共有</t>
+          <t>卡片共享</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>戦況報告共有</t>
+          <t>战况报告共享</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4993,7 +4993,7 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>時空激戦</t>
+          <t>时空激战</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>成就システム</t>
+          <t>成就系统</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>マップ募集</t>
+          <t>地图征集</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5207,7 +5207,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>ギルド戦</t>
+          <t>公会战</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>世界チャット</t>
+          <t>世界聊天</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5320,7 +5320,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>個人チャット</t>
+          <t>个人聊天</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>時空高層階直通</t>
+          <t>时空高层直通</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5433,7 +5433,7 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>ギルドメール</t>
+          <t>公会邮件</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>アイテム図鑑</t>
+          <t>项目图鉴</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5552,7 +5552,7 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>アリーナ5回スキップ</t>
+          <t>竞技场5次跳跃</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>ギルドボスに3回挑戦</t>
+          <t>挑战3次公会boss</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>戦闘ブック</t>
+          <t>战斗书</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>リアルタイム対戦</t>
+          <t>实时对战</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>1天賦リセット</t>
+          <t>1天赋重置</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5882,7 +5882,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>マイチーム</t>
+          <t>我的队伍</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>詐欺注意</t>
+          <t>诈骗注意事项</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>チップ</t>
+          <t>芯片</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6052,7 +6052,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>ショップ欠片星MAX表示</t>
+          <t>商店碎片星MAX显示</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6114,7 +6114,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>チッププラン</t>
+          <t>小费计划</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>装飾高速星アップ</t>
+          <t>装饰高速星星向上</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>装飾高速覚醒</t>
+          <t>装饰快速唤醒</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>チップ洗練</t>
+          <t>芯片精炼</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>チップガチャ表示</t>
+          <t>芯片转蛋显示</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>金貨極限モード</t>
+          <t>金币极限模式</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>経験値極限モード</t>
+          <t>经验值极限模式</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>分解画面で星MAXキャラを選択</t>
+          <t>在分解画面中选择星MAX角色</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>メール情報</t>
+          <t>电子邮件信息</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6609,7 +6609,7 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>クロスレイド</t>
+          <t>十字星</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
